--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N81_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N81_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.66059597272729</v>
+        <v>8.719846845568185</v>
       </c>
       <c r="D2" t="n">
-        <v>53.29423478527806</v>
+        <v>8.660313152607685</v>
       </c>
       <c r="E2" t="n">
-        <v>14.6346702371452</v>
+        <v>2.378133913536096</v>
       </c>
       <c r="F2" t="n">
-        <v>13.81806076891158</v>
+        <v>2.245434874948131</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.441441589514564</v>
+        <v>1.209234258296117</v>
       </c>
       <c r="D3" t="n">
-        <v>6.571290315029996</v>
+        <v>1.067834676192374</v>
       </c>
       <c r="E3" t="n">
-        <v>14.6346702371452</v>
+        <v>2.378133913536096</v>
       </c>
       <c r="F3" t="n">
-        <v>13.81806076891158</v>
+        <v>2.245434874948131</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.60292762879409</v>
+        <v>6.76047573967904</v>
       </c>
       <c r="D4" t="n">
-        <v>39.62897791939037</v>
+        <v>6.439708911900935</v>
       </c>
       <c r="E4" t="n">
-        <v>14.6346702371452</v>
+        <v>2.378133913536096</v>
       </c>
       <c r="F4" t="n">
-        <v>13.81806076891158</v>
+        <v>2.245434874948131</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>45.75561506159637</v>
+        <v>7.43528744750941</v>
       </c>
       <c r="D5" t="n">
-        <v>45.26111895312454</v>
+        <v>7.354931829882737</v>
       </c>
       <c r="E5" t="n">
-        <v>14.6346702371452</v>
+        <v>2.378133913536096</v>
       </c>
       <c r="F5" t="n">
-        <v>13.81806076891158</v>
+        <v>2.245434874948131</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.9564604510909</v>
+        <v>6.655424823302271</v>
       </c>
       <c r="D6" t="n">
-        <v>39.00895933255065</v>
+        <v>6.338955891539482</v>
       </c>
       <c r="E6" t="n">
-        <v>14.6346702371452</v>
+        <v>2.378133913536096</v>
       </c>
       <c r="F6" t="n">
-        <v>13.81806076891158</v>
+        <v>2.245434874948131</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>51.84999832897097</v>
+        <v>8.425624728457782</v>
       </c>
       <c r="D7" t="n">
-        <v>28.81642701838215</v>
+        <v>4.682669390487099</v>
       </c>
       <c r="E7" t="n">
-        <v>14.6346702371452</v>
+        <v>2.378133913536096</v>
       </c>
       <c r="F7" t="n">
-        <v>13.81806076891158</v>
+        <v>2.245434874948131</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>11.53505904814603</v>
+        <v>1.87444709532373</v>
       </c>
       <c r="D8" t="n">
-        <v>11.52039575717693</v>
+        <v>1.872064310541252</v>
       </c>
       <c r="E8" t="n">
-        <v>14.6346702371452</v>
+        <v>2.378133913536096</v>
       </c>
       <c r="F8" t="n">
-        <v>13.81806076891158</v>
+        <v>2.245434874948131</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>36.2125662251654</v>
+        <v>5.884542011589378</v>
       </c>
       <c r="D9" t="n">
-        <v>36.1331984772449</v>
+        <v>5.871644752552296</v>
       </c>
       <c r="E9" t="n">
-        <v>14.6346702371452</v>
+        <v>2.378133913536096</v>
       </c>
       <c r="F9" t="n">
-        <v>13.81806076891158</v>
+        <v>2.245434874948131</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>20.57405778752833</v>
+        <v>3.343284390473353</v>
       </c>
       <c r="D10" t="n">
-        <v>19.83791220743236</v>
+        <v>3.223660733707759</v>
       </c>
       <c r="E10" t="n">
-        <v>14.6346702371452</v>
+        <v>2.378133913536096</v>
       </c>
       <c r="F10" t="n">
-        <v>13.81806076891158</v>
+        <v>2.245434874948131</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>10.96907580876419</v>
+        <v>1.782474818924181</v>
       </c>
       <c r="D11" t="n">
-        <v>10.5538431812031</v>
+        <v>1.714999516945504</v>
       </c>
       <c r="E11" t="n">
-        <v>14.6346702371452</v>
+        <v>2.378133913536096</v>
       </c>
       <c r="F11" t="n">
-        <v>13.81806076891158</v>
+        <v>2.245434874948131</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>33.79537999540728</v>
+        <v>5.491749249253683</v>
       </c>
       <c r="D12" t="n">
-        <v>30.13290928905177</v>
+        <v>4.896597759470913</v>
       </c>
       <c r="E12" t="n">
-        <v>14.6346702371452</v>
+        <v>2.378133913536096</v>
       </c>
       <c r="F12" t="n">
-        <v>13.81806076891158</v>
+        <v>2.245434874948131</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>44.05153779222027</v>
+        <v>7.158374891235794</v>
       </c>
       <c r="D13" t="n">
-        <v>45.49793646114318</v>
+        <v>7.393414674935768</v>
       </c>
       <c r="E13" t="n">
-        <v>14.6346702371452</v>
+        <v>2.378133913536096</v>
       </c>
       <c r="F13" t="n">
-        <v>13.81806076891158</v>
+        <v>2.245434874948131</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>31.83861794218119</v>
+        <v>5.173775415604444</v>
       </c>
       <c r="D14" t="n">
-        <v>32.66729661177288</v>
+        <v>5.308435699413093</v>
       </c>
       <c r="E14" t="n">
-        <v>14.6346702371452</v>
+        <v>2.378133913536096</v>
       </c>
       <c r="F14" t="n">
-        <v>13.81806076891158</v>
+        <v>2.245434874948131</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>38.60228248140528</v>
+        <v>6.272870903228357</v>
       </c>
       <c r="D15" t="n">
-        <v>39.47445367915367</v>
+        <v>6.414598722862471</v>
       </c>
       <c r="E15" t="n">
-        <v>14.6346702371452</v>
+        <v>2.378133913536096</v>
       </c>
       <c r="F15" t="n">
-        <v>13.81806076891158</v>
+        <v>2.245434874948131</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
